--- a/survey_templates/036_most_likely_to_survey--survey_templates.xlsx
+++ b/survey_templates/036_most_likely_to_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>participant_input_1</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Most likely to win</t>
+          <t>How likely is it that you will win a prize?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>participant_input_2</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Most likely to win</t>
+          <t>How likely is it that you will be featured in a magazine?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,24 +561,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_input_3</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will be approached by a talent scout?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,24 +584,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>participant_input_4</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will be asked to be in a documentary?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -615,24 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>participant_input_5</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will be invited to a talk show?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -642,24 +630,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>participant_input_6</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will be asked to speak at a conference?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -669,24 +653,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_input_7</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will have a new hobby in the next year?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -696,24 +676,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>participant_input_8</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will have a new friend in the next year?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -723,24 +699,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>participant_input_9</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will have a new job in the next year?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,24 +722,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>participant_input_10</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will have a new skill in the next year?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -777,24 +745,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_input_11</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will have a new pet in the next year?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -804,376 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>participant_input_12</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
+          <t>How likely is it that you will be asked to write a book?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>participant_input_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>participant_input_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>participant_input_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>participant_input_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>participant_input_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>participant_input_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_input_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>participant_input_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>participant_input_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>participant_input_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>participant_input_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_input_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_input_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Predicted score</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Enter an integer</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1190,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1218,85 +827,1020 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>participant_input_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_am_very_likely_to_win</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I am very likely to win</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>participant_input_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_am_somewhat_likely_to_win</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I am somewhat likely to win</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>participant_input_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>i_am_not_likely_to_win</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>I am not likely to win</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>participant_input_2_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_have_no_chance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I have no chance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>participant_input_2_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_do_not_know</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_be_featured</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>I am very likely to be featured</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_be_featured</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to be featured</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_be_featured</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>I am not likely to be featured</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_be_approached</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>I am very likely to be approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_be_approached</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to be approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_be_approached</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>I am not likely to be approached</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_be_asked</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>I am very likely to be asked</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_be_asked</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to be asked</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_be_asked</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>I am not likely to be asked</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_be_invited</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>I am very likely to be invited</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_be_invited</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to be invited</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_be_invited</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>I am not likely to be invited</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_be_asked</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>I am very likely to be asked</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_be_asked</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to be asked</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_be_asked</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>I am not likely to be asked</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_get_a_new_hobby</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>I am very likely to get a new hobby</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_get_a_new_hobby</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to get a new hobby</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_get_a_new_hobby</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>I am not likely to get a new hobby</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_make_a_new_friend</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>I am very likely to make a new friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_make_a_new_friend</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to make a new friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_make_a_new_friend</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>I am not likely to make a new friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_get_a_new_job</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>I am very likely to get a new job</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_get_a_new_job</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to get a new job</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_get_a_new_job</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>I am not likely to get a new job</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_acquire_a_new_skill</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>I am very likely to acquire a new skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_acquire_a_new_skill</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to acquire a new skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_acquire_a_new_skill</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>I am not likely to acquire a new skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_get_a_new_pet</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>I am very likely to get a new pet</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_get_a_new_pet</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to get a new pet</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_get_a_new_pet</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>I am not likely to get a new pet</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>I do not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>i_am_very_likely_to_be_asked_to_write_a_book</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>I am very likely to be asked to write a book</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>i_am_somewhat_likely_to_be_asked_to_write_a_book</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>I am somewhat likely to be asked to write a book</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>i_am_not_likely_to_be_asked_to_write_a_book</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>I am not likely to be asked to write a book</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>i_have_no_chance</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>I have no chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>i_do_not_know</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>I do not know</t>
         </is>
       </c>
     </row>
